--- a/RoomImport/Пример импорта корявый.xlsx
+++ b/RoomImport/Пример импорта корявый.xlsx
@@ -573,7 +573,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>1000000</v>
+        <v>555555</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
@@ -590,13 +590,13 @@
       </c>
       <c r="L3" s="7" t="n"/>
       <c r="M3" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>35.67</v>
+        <v>100</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P3" s="7" t="n">
         <v>2</v>

--- a/RoomImport/Пример импорта корявый.xlsx
+++ b/RoomImport/Пример импорта корявый.xlsx
@@ -85,6 +85,9 @@
     <t>п3</t>
   </si>
   <si>
+    <t>лит. 1.1</t>
+  </si>
+  <si>
     <t>№ првк 1 -1-3</t>
   </si>
   <si>
@@ -104,6 +107,9 @@
   </si>
   <si>
     <t>№ првк 1 -1-6</t>
+  </si>
+  <si>
+    <t>офисное(8,9,10)</t>
   </si>
   <si>
     <t>№ првк 1 -2-3</t>
@@ -681,10 +687,10 @@
         <v>19</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>1</v>
@@ -725,7 +731,7 @@
         <v>1000009</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="s">
@@ -735,7 +741,7 @@
         <v>20</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L6" s="7" t="n">
         <v>1</v>
@@ -776,7 +782,7 @@
         <v>1000012</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="s">
@@ -786,7 +792,7 @@
         <v>20</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7" s="7" t="n">
         <v>1</v>
@@ -827,7 +833,7 @@
         <v>1000015</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="s">
@@ -837,7 +843,7 @@
         <v>20</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>1</v>
@@ -878,8 +884,8 @@
       <c r="F9" s="7" t="n">
         <v>1000000</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>1</v>
+      <c r="G9" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="s">
@@ -995,7 +1001,7 @@
         <v>20</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>2</v>
@@ -1048,7 +1054,7 @@
         <v>20</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L12" s="7" t="n">
         <v>2</v>
@@ -1103,7 +1109,7 @@
         <v>20</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L13" s="7" t="n">
         <v>2</v>
@@ -1158,7 +1164,7 @@
         <v>20</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L14" s="7" t="n">
         <v>2</v>
@@ -1276,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>20</v>
@@ -1300,7 +1306,7 @@
         <v>800006</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
@@ -1320,7 +1326,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>20</v>
@@ -1344,7 +1350,7 @@
         <v>800007</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
@@ -1364,10 +1370,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>-1</v>
@@ -1388,7 +1394,7 @@
         <v>800008</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
